--- a/data/14_trade_policy_compliance.xlsx
+++ b/data/14_trade_policy_compliance.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R323b331cdd4d411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R50c7ca49be484604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Re2ef0cb6c0e44792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R09e2a7c4b1d24024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rb80d5d80408b441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R9592349010374e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="Ra40003eecafa466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="R65c7ef1c60a54d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rf255a5b31f3d4cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R799d8bd49e3043e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R68f0884f6b3841b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="Re493ab6780784526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R76f1857190fb4050"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R17cb43223026473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R1826790396124241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="Rcd31d58495ea445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="Rfd056689ca82401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R6b9e8adcf1134f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="Rffcd2f975bbd4951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="R0f19d868271a4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R4dd3c55c73854b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rd6dcc6e1be944bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R3c3e10c1ae864cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="Rcaede5e8d5d44060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd41db6733b01482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rac8a0ab6ba464744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="Rf8dc3da768034aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R8e1715a8b6cf4c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="Ra5f269feb0804a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R3c71d2035dd84ca4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="Ra7533595df7d4b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R5fb595a3cd5f4f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="Re88432781041498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R81498536fc384bbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1329,7 +1329,9 @@
       <x:c r="G2" s="13" t="str">
         <x:v>9220641</x:v>
       </x:c>
-      <x:c r="H2" s="13"/>
+      <x:c r="H2" s="13" t="str">
+        <x:v>VESSEL_SAN_001</x:v>
+      </x:c>
       <x:c r="I2" s="13" t="str">
         <x:v>Russia</x:v>
       </x:c>
@@ -1340,7 +1342,7 @@
         <x:v>Linked to Transmorflot LLC in OFAC designation</x:v>
       </x:c>
       <x:c r="L2" s="13" t="str">
-        <x:v>No canonical vessel match in current v1.28 model; add on ingest</x:v>
+        <x:v>Canonical vessel integrated v1.30</x:v>
       </x:c>
       <x:c r="M2" s="13" t="str">
         <x:v>https://ofac.treasury.gov/recent-actions/20220508</x:v>
@@ -1368,7 +1370,9 @@
       <x:c r="G3" s="13" t="str">
         <x:v>9293117</x:v>
       </x:c>
-      <x:c r="H3" s="13"/>
+      <x:c r="H3" s="13" t="str">
+        <x:v>VESSEL_SAN_002</x:v>
+      </x:c>
       <x:c r="I3" s="13" t="str">
         <x:v>Russia-linked</x:v>
       </x:c>
@@ -1379,7 +1383,7 @@
         <x:v>Listed among UK Russia sanctions vessel targets</x:v>
       </x:c>
       <x:c r="L3" s="13" t="str">
-        <x:v>No canonical SUN vessel match found in current model</x:v>
+        <x:v>Canonical vessel integrated v1.30</x:v>
       </x:c>
       <x:c r="M3" s="13" t="str">
         <x:v>https://www.gov.uk/government/publications/list-of-russia-sanctions-targets-21-july-2025/list-of-russia-sanctions-targets-21-july-2025</x:v>
@@ -1407,7 +1411,9 @@
       <x:c r="G4" s="13" t="str">
         <x:v>9233234</x:v>
       </x:c>
-      <x:c r="H4" s="13"/>
+      <x:c r="H4" s="13" t="str">
+        <x:v>VESSEL_SAN_003</x:v>
+      </x:c>
       <x:c r="I4" s="13" t="str">
         <x:v>Iran-linked</x:v>
       </x:c>
@@ -1418,7 +1424,7 @@
         <x:v>Linked to Vroom Marine Venture FZE</x:v>
       </x:c>
       <x:c r="L4" s="13" t="str">
-        <x:v>UAE-linked manager entity is a useful compliance stress test</x:v>
+        <x:v>Canonical vessel integrated v1.30</x:v>
       </x:c>
       <x:c r="M4" s="13" t="str">
         <x:v>https://ofac.treasury.gov/recent-actions/20250430</x:v>
@@ -1446,7 +1452,9 @@
       <x:c r="G5" s="13" t="str">
         <x:v>9222649</x:v>
       </x:c>
-      <x:c r="H5" s="13"/>
+      <x:c r="H5" s="13" t="str">
+        <x:v>VESSEL_SAN_004</x:v>
+      </x:c>
       <x:c r="I5" s="13" t="str">
         <x:v>Iran-linked</x:v>
       </x:c>
@@ -1457,7 +1465,7 @@
         <x:v>Linked to Manarat Alkhaleej Marine Services FZE</x:v>
       </x:c>
       <x:c r="L5" s="13" t="str">
-        <x:v>Tests UAE-registered / UAE-linked counterparties in sanctions graph</x:v>
+        <x:v>Canonical vessel integrated v1.30</x:v>
       </x:c>
       <x:c r="M5" s="13" t="str">
         <x:v>https://ofac.treasury.gov/recent-actions/20260206</x:v>
@@ -1485,7 +1493,9 @@
       <x:c r="G6" s="13" t="str">
         <x:v>9253117</x:v>
       </x:c>
-      <x:c r="H6" s="13"/>
+      <x:c r="H6" s="13" t="str">
+        <x:v>VESSEL_SAN_005</x:v>
+      </x:c>
       <x:c r="I6" s="13" t="str">
         <x:v>Iran-linked</x:v>
       </x:c>
@@ -1496,7 +1506,7 @@
         <x:v>Linked to Laurel Shipping Ltd</x:v>
       </x:c>
       <x:c r="L6" s="13" t="str">
-        <x:v>Representative shadow-fleet / oil-trade designation</x:v>
+        <x:v>Canonical vessel integrated v1.30</x:v>
       </x:c>
       <x:c r="M6" s="13" t="str">
         <x:v>https://ofac.treasury.gov/recent-actions/20260424</x:v>
@@ -1560,9 +1570,11 @@
       <x:c r="D2" s="13" t="str">
         <x:v>Vessel</x:v>
       </x:c>
-      <x:c r="E2" s="13"/>
+      <x:c r="E2" s="13" t="str">
+        <x:v>VESSEL_SAN_001</x:v>
+      </x:c>
       <x:c r="F2" s="13" t="str">
-        <x:v>New canonical vessel required</x:v>
+        <x:v>Canonical vessel integrated</x:v>
       </x:c>
       <x:c r="G2" s="13" t="str">
         <x:v>High</x:v>
@@ -1584,9 +1596,11 @@
       <x:c r="D3" s="13" t="str">
         <x:v>Vessel</x:v>
       </x:c>
-      <x:c r="E3" s="13"/>
+      <x:c r="E3" s="13" t="str">
+        <x:v>VESSEL_SAN_002</x:v>
+      </x:c>
       <x:c r="F3" s="13" t="str">
-        <x:v>New canonical vessel required / reconcile with IRINI record</x:v>
+        <x:v>Canonical vessel integrated</x:v>
       </x:c>
       <x:c r="G3" s="13" t="str">
         <x:v>High</x:v>
@@ -1608,9 +1622,11 @@
       <x:c r="D4" s="13" t="str">
         <x:v>Company</x:v>
       </x:c>
-      <x:c r="E4" s="13"/>
+      <x:c r="E4" s="13" t="str">
+        <x:v>COMP_VROOM_MARINE</x:v>
+      </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>New canonical company required</x:v>
+        <x:v>Canonical company integrated</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
         <x:v>High</x:v>
@@ -1632,9 +1648,11 @@
       <x:c r="D5" s="13" t="str">
         <x:v>Company</x:v>
       </x:c>
-      <x:c r="E5" s="13"/>
+      <x:c r="E5" s="13" t="str">
+        <x:v>COMP_MANARAT_ALKHALEEJ</x:v>
+      </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>New canonical company required</x:v>
+        <x:v>Canonical company integrated</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
         <x:v>High</x:v>
@@ -1656,15 +1674,147 @@
       <x:c r="D6" s="13" t="str">
         <x:v>Vessel</x:v>
       </x:c>
-      <x:c r="E6" s="13"/>
+      <x:c r="E6" s="13" t="str">
+        <x:v>VESSEL_SAN_005</x:v>
+      </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>New canonical vessel required</x:v>
+        <x:v>Canonical vessel integrated</x:v>
       </x:c>
       <x:c r="G6" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
         <x:v>Representative Iran oil / shadow fleet case.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>SLINK_006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>DES_001</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>MG-FLOT LLC</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>COMP_MG_FLOT</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Canonical company integrated</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Current owner/manager linked to LADY MARIIA; formerly Transmorflot LLC.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>SLINK_007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>DES_002</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Wavewhisper Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>COMP_WAVEWHISPER</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Canonical associated company integrated</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>UK sanctions list identifies current owner/operator of SUN; this link does not itself assert a separate company designation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>SLINK_008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>DES_003</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>ELOISE</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>VESSEL_SAN_003</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Canonical vessel integrated</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Target vessel for OFAC designation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>SLINK_009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>DES_004</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>AL SAFA</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>VESSEL_SAN_004</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>Canonical vessel integrated</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Target vessel for OFAC designation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>SLINK_010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>DES_005</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Laurel Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>COMP_LAUREL_SHIPPING</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Canonical associated company integrated</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>OFAC designation links ANSHUN II to Laurel Shipping Ltd.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/14_trade_policy_compliance.xlsx
+++ b/data/14_trade_policy_compliance.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R6b9e8adcf1134f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="Rffcd2f975bbd4951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="R0f19d868271a4542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R4dd3c55c73854b66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rd6dcc6e1be944bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R3c3e10c1ae864cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="Rcaede5e8d5d44060"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd41db6733b01482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rac8a0ab6ba464744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="Rf8dc3da768034aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R8e1715a8b6cf4c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="Ra5f269feb0804a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R3c71d2035dd84ca4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="Ra7533595df7d4b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R5fb595a3cd5f4f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="Re88432781041498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R81498536fc384bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R5c4dfbe7c44a4821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R75681e4871a84cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Rffe7d8d93f5b4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R2fa9329b9643485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Ref55156868384b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="Rf8d5278ea6d843d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R807053e44dd34efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd005a9f9fca04906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="R583b374ecdeb47a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R93a2eb84965245be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R9768a1762f34438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5a4fddcd40084625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R4c9d9c4918ec4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R316fa931ae8a4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7159aadf7d0c471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="R2242d0e6d0024f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R209d5474b71043f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1512,6 +1512,129 @@
         <x:v>https://ofac.treasury.gov/recent-actions/20260424</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>DES_006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>AUTH_OFAC</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>SANPROG_IRAN_13902</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>2025-07-30</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>CHARMINAR</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>9318022</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Iran-linked</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Designated / SDN</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>OFAC added CHARMINAR under IRAN-EO13902; linked to ALGAE SHIP CHARTER - FZCO</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>Canonical vessel integrated v1.32</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20250730_33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>DES_007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>AUTH_OFAC</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>SANPROG_IRAN_13846</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>2025-11-20</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>AQUARIS / current RIESCO</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>9251822</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Iran-linked</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Designated / SDN</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>OFAC added AQUARIS (IMO 9251822), later renamed RIESCO; linked to Arkadia Maritime Incorporated</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>Canonical vessel integrated v1.32</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20251120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>DES_008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>AUTH_OFAC</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>SANPROG_IRAN_13846</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>2018-11-05</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>DERYA</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>9569700</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Iran-linked / NITC</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Designated / SDN</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>OFAC SDN vessel linked to National Iranian Tanker Company; later flag update to Iran</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>Canonical vessel integrated v1.32</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>https://sanctionssearch.ofac.treas.gov/Details.aspx?id=25714</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1817,6 +1940,188 @@
         <x:v>OFAC designation links ANSHUN II to Laurel Shipping Ltd.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>SLINK_011</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>DES_006</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>CHARMINAR</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Canonical vessel integrated</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>OFAC-designated vessel; CENTCOM struck 8 Sep 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>SLINK_012</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>DES_006</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Canonical company integrated</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>OFAC designation-linked company.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>SLINK_013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>DES_007</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>RIESCO / former AQUARIS</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Canonical vessel integrated</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Same IMO 9251822; rename preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>SLINK_014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>DES_007</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Arkadia Maritime Incorporated</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>COMP_ARKADIA_MARITIME</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Canonical company integrated</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>OFAC linked owner at designation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>SLINK_015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>DES_008</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>DERYA</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Canonical vessel integrated</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>OFAC / NITC-linked vessel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>SLINK_016</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>DES_008</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>National Iranian Tanker Company</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>COMP_NITC</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Existing canonical company</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>OFAC-linked NITC exposure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>SLINK_017</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>DES_008</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Kharg / Iranian crude export network</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>System / geography</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>System-linked</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Operational context, not a separate designation target.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2347,6 +2652,62 @@
       </x:c>
       <x:c r="D16" s="13" t="str">
         <x:v>https://ofac.treasury.gov/recent-actions/20260424</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>SRC132_POL_001</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>CHARMINAR designation</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20250730_33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>SRC132_POL_002</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>AQUARIS / RIESCO IMO 9251822 designation</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>https://ofac.treasury.gov/recent-actions/20251120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>SRC132_POL_003</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>US Treasury OFAC</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>DERYA / NITC designation</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>https://sanctionssearch.ofac.treas.gov/Details.aspx?id=25714</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SRC132_POL_004</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>U.S. Central Command</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Kinetic strikes on five Iran-linked tankers</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/14_trade_policy_compliance.xlsx
+++ b/data/14_trade_policy_compliance.xlsx
@@ -2,23 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R5c4dfbe7c44a4821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R75681e4871a84cb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Rffe7d8d93f5b4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R2fa9329b9643485a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Ref55156868384b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="Rf8d5278ea6d843d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R807053e44dd34efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd005a9f9fca04906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="R583b374ecdeb47a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R93a2eb84965245be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R9768a1762f34438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5a4fddcd40084625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R4c9d9c4918ec4297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R316fa931ae8a4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7159aadf7d0c471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="R2242d0e6d0024f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R209d5474b71043f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="Rc94c3e2e60d34fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R96e38f6e643e4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Ra838e40942c147e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R5a8d460a3ad14dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rd5aa5fc156304101"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R02bc5867823547a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R1ca1679babea4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="R5825918ea95e4712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rd19cdc9ef0e642ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="Rf615e41ade8f41cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R8ea55af4fbed4833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5ff7150aa3db4307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R479a9e7a351b4fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="Rf8a6e2ab3891459d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7a1862f9f00d4634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="Ra55aee01324e4fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R2316cd7b2856432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Regimes" sheetId="18" r:id="R3e2c073b2791454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Designations" sheetId="19" r:id="Rd1dd6c367821448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Exposure" sheetId="20" r:id="Ra41a9bed86324138"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -52,8 +55,14 @@
       <x:color rgb="FF0B1F33"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8B45A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -70,6 +79,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF11161A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -78,7 +92,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -122,6 +136,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2278,6 +2298,29 @@
         <x:v>Variable</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>WATCH_PGSA</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Operational compliance regime</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>PGSA non-compliant vessel list</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>Iranian / contested operational authority</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str">
+        <x:v>Keep separate from OFAC/EU/UK/UN sanctions; IMO-first vessel identity</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
+        <x:v>Potential fines, detention, cargo confiscation, future transit restriction and secondary commercial exposure</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2931,6 +2974,323 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Regime ID</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>Regime</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>Authority / Sponsor</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>Jurisdiction / Geography</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>Regime Type</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>Effective / Observed From</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>Enforcement Mechanisms</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>Legal / Analytical Note</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>PGSA Maritime Compliance Regime</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>Persian Gulf Strait Authority / Iran</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Strait of Hormuz and future-transit exposure</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="str">
+        <x:v>Operational maritime compliance / blacklist</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>Active / reported</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>Fine; detention; cargo confiscation; transit restriction; counterparty exposure</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>Do not represent as equivalent to OFAC/EU/UK/UN sanctions; asserted jurisdiction is contested.</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
+        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
+        <x:v>REGIME_DGS_CASUALTY</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>India Marine Casualty / Safety Regime</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>Directorate General of Shipping</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>India / Indian shipping</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>Marine safety / casualty investigation</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="G3" s="10"/>
+      <x:c r="H3" s="10" t="str">
+        <x:v>Investigation; circulars; safety guidance; regulatory follow-up</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>Regulatory safety regime, not a sanctions/watchlist regime.</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>https://www.dgshipping.gov.in/</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Designation ID</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>Regime ID</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>Target Type</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>Target ID</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>Target Name</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>IMO / Identifier</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>Direct / Indirect</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>Reason / Basis</x:v>
+      </x:c>
+      <x:c r="K1" s="26" t="str">
+        <x:v>Verification</x:v>
+      </x:c>
+      <x:c r="L1" s="26" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="M1" s="26" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="10" t="str">
+        <x:v>CD_PGSA_001</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="str">
+        <x:v>VESSEL_00024</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>Mraweh</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>9074638</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>Listed / reported</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
+        <x:v>Original PGSA non-compliant vessel list</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="str">
+        <x:v>IMO matched</x:v>
+      </x:c>
+      <x:c r="L2" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>Canonical ADNOC L&amp;S vessel already in model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
+        <x:v>CD_PGSA_002</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>VESSEL_00075</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>Tarif</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>9828390</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="str">
+        <x:v>Listed / reported</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>Reported list expansion</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str">
+        <x:v>IMO matched</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>Canonical ADNOC L&amp;S vessel already in model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>CD_PGSA_003</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>VESSEL_SEC_001</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>GasLog Shanghai</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>9600528</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>Listed / reported</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>Original PGSA non-compliant vessel list</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>IMO matched</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>STS relationship modeled separately.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="10" t="str">
+        <x:v>CD_PGSA_004</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
+        <x:v>VESSEL_SEC_002</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>Al Rekayyat</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>9397339</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>Listed / reported</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="str">
+        <x:v>Original PGSA non-compliant vessel list</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="str">
+        <x:v>IMO matched</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>STS relationship modeled separately.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3521,6 +3881,216 @@
       </x:c>
       <x:c r="F29" s="13" t="str">
         <x:v>In force / phased implementation</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Exposure ID</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>Regime ID</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>Source Vessel ID</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>Source Vessel</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>Counterparty / Related Entity</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>Related Entity Type</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>Relationship</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>Event / Geography</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>Exposure Type</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="K1" s="26" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="L1" s="26" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="M1" s="26" t="str">
+        <x:v>Analytical Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="10" t="str">
+        <x:v>CEXP_PGSA_001</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>VESSEL_SEC_001</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>GasLog Shanghai</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="str">
+        <x:v>GasLog Savannah</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>Ship-to-ship transfer</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>Off Oman / outside Hormuz</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>Potential secondary PGSA exposure</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
+        <x:v>Observed interaction / exposure requires monitoring</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="L2" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>Listed vessel transferred LNG to GasLog Savannah; future Hormuz exposure is the key compliance question.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
+        <x:v>CEXP_PGSA_002</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>VESSEL_SEC_002</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>Al Rekayyat</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>Tembek</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>Ship-to-ship transfer</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="str">
+        <x:v>Off Oman / outside Hormuz</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>Potential secondary PGSA exposure</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>Observed interaction / exposure requires monitoring</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>Listed vessel transferred LNG to Tembek before onward carriage to India.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
+        <x:v>CEXP_PGSA_003</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>VESSEL_00024</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>Mraweh</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>LNG Enugu</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>Ship-to-ship transfer</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>Off Oman / outside Hormuz</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>Potential secondary PGSA exposure</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>Observed interaction / exposure requires monitoring</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>Listed ADNOC-controlled vessel transferred LNG to LNG Enugu before onward movement toward Japan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="10" t="str">
+        <x:v>CEXP_PGSA_004</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>REGIME_PGSA</x:v>
+      </x:c>
+      <x:c r="C5" s="10"/>
+      <x:c r="D5" s="10"/>
+      <x:c r="E5" s="10" t="str">
+        <x:v>Indian refiners / global energy company</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>Commercial counterparty</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>Vessel avoidance / chartering decision</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>India / Gulf energy trade</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="str">
+        <x:v>Behavioural compliance effect</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="str">
+        <x:v>Reported market response</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="str">
+        <x:v>Medium-High</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>Commercial actors reportedly avoided listed vessels; preserve source-level caveats and do not infer unnamed companies.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/14_trade_policy_compliance.xlsx
+++ b/data/14_trade_policy_compliance.xlsx
@@ -2,26 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="Rc94c3e2e60d34fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R96e38f6e643e4ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Ra838e40942c147e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R5a8d460a3ad14dc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rd5aa5fc156304101"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R02bc5867823547a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R1ca1679babea4631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="R5825918ea95e4712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rd19cdc9ef0e642ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="Rf615e41ade8f41cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R8ea55af4fbed4833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5ff7150aa3db4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R479a9e7a351b4fed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="Rf8a6e2ab3891459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7a1862f9f00d4634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="Ra55aee01324e4fe2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R2316cd7b2856432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Regimes" sheetId="18" r:id="R3e2c073b2791454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Designations" sheetId="19" r:id="Rd1dd6c367821448b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Exposure" sheetId="20" r:id="Ra41a9bed86324138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R5c4dfbe7c44a4821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R75681e4871a84cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Rffe7d8d93f5b4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R2fa9329b9643485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Ref55156868384b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="Rf8d5278ea6d843d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R807053e44dd34efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd005a9f9fca04906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="R583b374ecdeb47a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R93a2eb84965245be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R9768a1762f34438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5a4fddcd40084625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R4c9d9c4918ec4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R316fa931ae8a4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7159aadf7d0c471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="R2242d0e6d0024f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R209d5474b71043f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,7 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -55,14 +52,8 @@
       <x:color rgb="FF0B1F33"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFD8B45A"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -79,11 +70,6 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF11161A"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -92,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -136,12 +122,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2298,29 +2278,6 @@
         <x:v>Variable</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="10" t="str">
-        <x:v>WATCH_PGSA</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>Operational compliance regime</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
-        <x:v>PGSA non-compliant vessel list</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="str">
-        <x:v>Iranian / contested operational authority</x:v>
-      </x:c>
-      <x:c r="E7" s="10" t="str">
-        <x:v>Keep separate from OFAC/EU/UK/UN sanctions; IMO-first vessel identity</x:v>
-      </x:c>
-      <x:c r="F7" s="10" t="str">
-        <x:v>Potential fines, detention, cargo confiscation, future transit restriction and secondary commercial exposure</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2974,323 +2931,6 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="26" t="str">
-        <x:v>Regime ID</x:v>
-      </x:c>
-      <x:c r="B1" s="26" t="str">
-        <x:v>Regime</x:v>
-      </x:c>
-      <x:c r="C1" s="26" t="str">
-        <x:v>Authority / Sponsor</x:v>
-      </x:c>
-      <x:c r="D1" s="26" t="str">
-        <x:v>Jurisdiction / Geography</x:v>
-      </x:c>
-      <x:c r="E1" s="26" t="str">
-        <x:v>Regime Type</x:v>
-      </x:c>
-      <x:c r="F1" s="26" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="G1" s="26" t="str">
-        <x:v>Effective / Observed From</x:v>
-      </x:c>
-      <x:c r="H1" s="26" t="str">
-        <x:v>Enforcement Mechanisms</x:v>
-      </x:c>
-      <x:c r="I1" s="26" t="str">
-        <x:v>Legal / Analytical Note</x:v>
-      </x:c>
-      <x:c r="J1" s="26" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>PGSA Maritime Compliance Regime</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>Persian Gulf Strait Authority / Iran</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>Strait of Hormuz and future-transit exposure</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>Operational maritime compliance / blacklist</x:v>
-      </x:c>
-      <x:c r="F2" s="10" t="str">
-        <x:v>Active / reported</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>Fine; detention; cargo confiscation; transit restriction; counterparty exposure</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>Do not represent as equivalent to OFAC/EU/UK/UN sanctions; asserted jurisdiction is contested.</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>https://www.powerncorridors.com/the-pgsa-blacklist-irans-expanding-maritime-compliance-regime-in-the-strait-of-hormuz/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="10" t="str">
-        <x:v>REGIME_DGS_CASUALTY</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>India Marine Casualty / Safety Regime</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>Directorate General of Shipping</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="str">
-        <x:v>India / Indian shipping</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>Marine safety / casualty investigation</x:v>
-      </x:c>
-      <x:c r="F3" s="10" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="G3" s="10"/>
-      <x:c r="H3" s="10" t="str">
-        <x:v>Investigation; circulars; safety guidance; regulatory follow-up</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>Regulatory safety regime, not a sanctions/watchlist regime.</x:v>
-      </x:c>
-      <x:c r="J3" s="10" t="str">
-        <x:v>https://www.dgshipping.gov.in/</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="26" t="str">
-        <x:v>Designation ID</x:v>
-      </x:c>
-      <x:c r="B1" s="26" t="str">
-        <x:v>Regime ID</x:v>
-      </x:c>
-      <x:c r="C1" s="26" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="D1" s="26" t="str">
-        <x:v>Target Type</x:v>
-      </x:c>
-      <x:c r="E1" s="26" t="str">
-        <x:v>Target ID</x:v>
-      </x:c>
-      <x:c r="F1" s="26" t="str">
-        <x:v>Target Name</x:v>
-      </x:c>
-      <x:c r="G1" s="26" t="str">
-        <x:v>IMO / Identifier</x:v>
-      </x:c>
-      <x:c r="H1" s="26" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="I1" s="26" t="str">
-        <x:v>Direct / Indirect</x:v>
-      </x:c>
-      <x:c r="J1" s="26" t="str">
-        <x:v>Reason / Basis</x:v>
-      </x:c>
-      <x:c r="K1" s="26" t="str">
-        <x:v>Verification</x:v>
-      </x:c>
-      <x:c r="L1" s="26" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="M1" s="26" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="10" t="str">
-        <x:v>CD_PGSA_001</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>VESSEL_00024</x:v>
-      </x:c>
-      <x:c r="F2" s="10" t="str">
-        <x:v>Mraweh</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>9074638</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>Listed / reported</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>Original PGSA non-compliant vessel list</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>IMO matched</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>Canonical ADNOC L&amp;S vessel already in model.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="10" t="str">
-        <x:v>CD_PGSA_002</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>VESSEL_00075</x:v>
-      </x:c>
-      <x:c r="F3" s="10" t="str">
-        <x:v>Tarif</x:v>
-      </x:c>
-      <x:c r="G3" s="10" t="str">
-        <x:v>9828390</x:v>
-      </x:c>
-      <x:c r="H3" s="10" t="str">
-        <x:v>Listed / reported</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="J3" s="10" t="str">
-        <x:v>Reported list expansion</x:v>
-      </x:c>
-      <x:c r="K3" s="10" t="str">
-        <x:v>IMO matched</x:v>
-      </x:c>
-      <x:c r="L3" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>Canonical ADNOC L&amp;S vessel already in model.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="10" t="str">
-        <x:v>CD_PGSA_003</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E4" s="10" t="str">
-        <x:v>VESSEL_SEC_001</x:v>
-      </x:c>
-      <x:c r="F4" s="10" t="str">
-        <x:v>GasLog Shanghai</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>9600528</x:v>
-      </x:c>
-      <x:c r="H4" s="10" t="str">
-        <x:v>Listed / reported</x:v>
-      </x:c>
-      <x:c r="I4" s="10" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="J4" s="10" t="str">
-        <x:v>Original PGSA non-compliant vessel list</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str">
-        <x:v>IMO matched</x:v>
-      </x:c>
-      <x:c r="L4" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>STS relationship modeled separately.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="10" t="str">
-        <x:v>CD_PGSA_004</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="str">
-        <x:v>VESSEL_SEC_002</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="str">
-        <x:v>Al Rekayyat</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str">
-        <x:v>9397339</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="str">
-        <x:v>Listed / reported</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="str">
-        <x:v>Direct</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="str">
-        <x:v>Original PGSA non-compliant vessel list</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="str">
-        <x:v>IMO matched</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>STS relationship modeled separately.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3881,216 +3521,6 @@
       </x:c>
       <x:c r="F29" s="13" t="str">
         <x:v>In force / phased implementation</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="26" t="str">
-        <x:v>Exposure ID</x:v>
-      </x:c>
-      <x:c r="B1" s="26" t="str">
-        <x:v>Regime ID</x:v>
-      </x:c>
-      <x:c r="C1" s="26" t="str">
-        <x:v>Source Vessel ID</x:v>
-      </x:c>
-      <x:c r="D1" s="26" t="str">
-        <x:v>Source Vessel</x:v>
-      </x:c>
-      <x:c r="E1" s="26" t="str">
-        <x:v>Counterparty / Related Entity</x:v>
-      </x:c>
-      <x:c r="F1" s="26" t="str">
-        <x:v>Related Entity Type</x:v>
-      </x:c>
-      <x:c r="G1" s="26" t="str">
-        <x:v>Relationship</x:v>
-      </x:c>
-      <x:c r="H1" s="26" t="str">
-        <x:v>Event / Geography</x:v>
-      </x:c>
-      <x:c r="I1" s="26" t="str">
-        <x:v>Exposure Type</x:v>
-      </x:c>
-      <x:c r="J1" s="26" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="K1" s="26" t="str">
-        <x:v>Confidence</x:v>
-      </x:c>
-      <x:c r="L1" s="26" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="M1" s="26" t="str">
-        <x:v>Analytical Note</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="10" t="str">
-        <x:v>CEXP_PGSA_001</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>VESSEL_SEC_001</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>GasLog Shanghai</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>GasLog Savannah</x:v>
-      </x:c>
-      <x:c r="F2" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>Ship-to-ship transfer</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>Off Oman / outside Hormuz</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>Potential secondary PGSA exposure</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>Observed interaction / exposure requires monitoring</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>Listed vessel transferred LNG to GasLog Savannah; future Hormuz exposure is the key compliance question.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="10" t="str">
-        <x:v>CEXP_PGSA_002</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>VESSEL_SEC_002</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="str">
-        <x:v>Al Rekayyat</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>Tembek</x:v>
-      </x:c>
-      <x:c r="F3" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="G3" s="10" t="str">
-        <x:v>Ship-to-ship transfer</x:v>
-      </x:c>
-      <x:c r="H3" s="10" t="str">
-        <x:v>Off Oman / outside Hormuz</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>Potential secondary PGSA exposure</x:v>
-      </x:c>
-      <x:c r="J3" s="10" t="str">
-        <x:v>Observed interaction / exposure requires monitoring</x:v>
-      </x:c>
-      <x:c r="K3" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="L3" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>Listed vessel transferred LNG to Tembek before onward carriage to India.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="10" t="str">
-        <x:v>CEXP_PGSA_003</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="str">
-        <x:v>VESSEL_00024</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>Mraweh</x:v>
-      </x:c>
-      <x:c r="E4" s="10" t="str">
-        <x:v>LNG Enugu</x:v>
-      </x:c>
-      <x:c r="F4" s="10" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>Ship-to-ship transfer</x:v>
-      </x:c>
-      <x:c r="H4" s="10" t="str">
-        <x:v>Off Oman / outside Hormuz</x:v>
-      </x:c>
-      <x:c r="I4" s="10" t="str">
-        <x:v>Potential secondary PGSA exposure</x:v>
-      </x:c>
-      <x:c r="J4" s="10" t="str">
-        <x:v>Observed interaction / exposure requires monitoring</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="L4" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>Listed ADNOC-controlled vessel transferred LNG to LNG Enugu before onward movement toward Japan.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="10" t="str">
-        <x:v>CEXP_PGSA_004</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>REGIME_PGSA</x:v>
-      </x:c>
-      <x:c r="C5" s="10"/>
-      <x:c r="D5" s="10"/>
-      <x:c r="E5" s="10" t="str">
-        <x:v>Indian refiners / global energy company</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="str">
-        <x:v>Commercial counterparty</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str">
-        <x:v>Vessel avoidance / chartering decision</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="str">
-        <x:v>India / Gulf energy trade</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="str">
-        <x:v>Behavioural compliance effect</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="str">
-        <x:v>Reported market response</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="str">
-        <x:v>Medium-High</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>Commercial actors reportedly avoided listed vessels; preserve source-level caveats and do not infer unnamed companies.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/14_trade_policy_compliance.xlsx
+++ b/data/14_trade_policy_compliance.xlsx
@@ -2,23 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R5c4dfbe7c44a4821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R75681e4871a84cb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="Rffe7d8d93f5b4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R2fa9329b9643485a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Ref55156868384b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="Rf8d5278ea6d843d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R807053e44dd34efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="Rd005a9f9fca04906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="R583b374ecdeb47a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R93a2eb84965245be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R9768a1762f34438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R5a4fddcd40084625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="R4c9d9c4918ec4297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R316fa931ae8a4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R7159aadf7d0c471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="R2242d0e6d0024f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="R209d5474b71043f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Agreements" sheetId="1" r:id="R48dcab802de34132"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Parties" sheetId="2" r:id="R8743931ba2764d7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Asset Links" sheetId="3" r:id="R3c080cc08665485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement Company Links" sheetId="4" r:id="R88f672cf8f5f42ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tariff Coverage" sheetId="5" r:id="Rdfb2b46919f74c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HS Product Tests" sheetId="6" r:id="R13ed524c68444e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules of Origin" sheetId="7" r:id="R3ae627045e6143a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customs &amp; Procurement" sheetId="8" r:id="R1c78d4b7c56f46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Remedies &amp; Restrictions" sheetId="9" r:id="Rc1f3c519036d4b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Authorities" sheetId="10" r:id="R1219441f538d44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Programmes" sheetId="11" r:id="R0e18444b88684a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Designations" sheetId="12" r:id="R1f8a03afc56c44eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanctions Entity Links" sheetId="13" r:id="Rd1fd85bc18f7450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist Taxonomy" sheetId="14" r:id="R420880b7c9ac4b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Interaction Rules" sheetId="15" r:id="R9868c1e5d4a048da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="16" r:id="R6e93255e9cf04557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="17" r:id="Rcdb84d6be75e4225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Advisories" sheetId="18" r:id="R4dea4ab809e54b4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +54,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -70,6 +71,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -78,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -122,6 +128,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2931,6 +2943,153 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="35" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="50" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>Advisory ID</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>Authority / Source</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>Jurisdiction</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>Issue</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>Rule / Warning</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>Trade / Operational Effect</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>Risk Type</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="K1" s="26" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="L1" s="26" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="M1" s="26" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="10" t="str">
+        <x:v>CADV_001</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>Maritime and Port Authority of Singapore</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="str">
+        <x:v>Maritime / Port</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>False vessel identity / ownership / cargo / trading-history data</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>Port users must submit accurate information and verify registrations; enforcement action may follow deliberate false or misleading filings.</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>Potential port-clearance delay/refusal, agent/owner liability, sanctions screening and bunkering transaction friction.</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>Compliance / sanctions / vessel identity</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="str">
+        <x:v>SRC_SEC_010</x:v>
+      </x:c>
+      <x:c r="L2" s="10" t="str">
+        <x:v>https://www.mpa.gov.sg/media-centre</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>MPA Port Marine Circular No. 10 of 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
+        <x:v>CADV_002</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>Ship &amp; Bunker / Windward data</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>Maritime / Bunkering</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>Fraudulent registries and AIS spoofing</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>Traditional flag-certificate and AIS-history checks may be unreliable; suppliers face growing sanctions exposure.</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="str">
+        <x:v>Higher KYC burden, bunker refusals, counterparty risk and transaction delays.</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>Sanctions evasion / identity fraud / AIS manipulation</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
+        <x:v>Active trend</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str">
+        <x:v>SRC_SEC_011</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str">
+        <x:v>https://shipandbunker.com/news/world/312418-feature-bunker-suppliers-can-no-longer-trust-two-key-sanctions-checks</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>Article cites 275 tankers on fraudulent registry flags in Q2 and 1.24m false STS AIS meetings in the quarter.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
